--- a/data/business/game_targets.xlsx
+++ b/data/business/game_targets.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="game_targets" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_targets" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'game_targets'!$A$1:$E$1002</definedName>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1002"/>
+  <dimension ref="A1:E1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -17462,23 +17462,6 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="1002">
-      <c r="A1002" t="n">
-        <v>9000001</v>
-      </c>
-      <c r="B1002" t="n">
-        <v>37250</v>
-      </c>
-      <c r="C1002" t="n">
-        <v>17300</v>
-      </c>
-      <c r="D1002" t="n">
-        <v>281000</v>
-      </c>
-      <c r="E1002" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:E1002"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
